--- a/backtest_runs/20260410_193731/by_symbol/ANL/ANL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ANL/ANL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1518.659999999988</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98481.34000000001</v>
@@ -633,7 +633,7 @@
         <v>-1168.199999999996</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100700.92</v>
@@ -679,7 +679,7 @@
         <v>-11682</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>89018.92000000001</v>
@@ -817,7 +817,7 @@
         <v>-584.0999999999875</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>93574.90000000001</v>
@@ -909,7 +909,7 @@
         <v>-934.5600000000009</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>93341.26000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-233.639999999995</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>95444.02000000002</v>
@@ -1231,7 +1231,7 @@
         <v>-3971.879999999998</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>105256.9</v>
@@ -1277,7 +1277,7 @@
         <v>-5256.900000000012</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>100000</v>
@@ -1323,7 +1323,7 @@
         <v>-1752.299999999983</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>98247.70000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-1635.479999999986</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>99415.90000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-4439.160000000009</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>105607.36</v>
